--- a/assets/constructions/examples/ctd_arbm_tappingchuck.xlsx
+++ b/assets/constructions/examples/ctd_arbm_tappingchuck.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,11 +604,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK40-VER32-106</t>
+          <t>BT40-TPG1024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -618,17 +638,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Патроны SK-VER для синхронизированного резьбонарезания</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>106</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>Патроны BT-TPG для жесткого резьбонарезания</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2" t="n">
+        <v>75</v>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -642,12 +664,12 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>DER_BLC-32</t>
+          <t>DER_BRC-1024</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>DER_VER:32</t>
+          <t>DER_TPE:1024</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -674,16 +696,16 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>DIN_69871:SK40</t>
+          <t>JIS_B_6339_MAS_403:BT40</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AG2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -693,11 +715,17 @@
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
+      <c r="AJ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BT50-VER32-109</t>
+          <t>C40-VER40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -707,18 +735,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Патроны BT-VER для синхронизированного резьбонарезания</t>
+          <t>Патроны C-VER для синхронизированного резьбонарезания</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>109</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>72</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F3" t="n">
+        <v>80</v>
+      </c>
+      <c r="G3" t="n">
+        <v>87</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -729,14 +761,10 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>DER_BLC-32</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>DER_VER:32</t>
+          <t>DER_VER:40</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -745,14 +773,10 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>7</v>
-      </c>
-      <c r="X3" t="n">
-        <v>16</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
@@ -763,17 +787,15 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT50</t>
+          <t>HB-40</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
+        <v>2.98</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
@@ -782,34 +804,40 @@
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
+      <c r="AJ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT50AD/B-SYTER20-100</t>
+          <t>SK40-TPM830</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SYNCHRO TAPPING CHUCK (ER TYPE)</t>
+          <t>Патроны для резьбонарезания с осевой компенсацией SK-TPM со сменными втулками с предохранительной муфтой</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>143.6</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G4" t="n">
-        <v>42</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>143.6</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>66</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -820,56 +848,78 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>DER_BRC-830</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ER25-SQ</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
+          <t>DER_TPD:830</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>DEREK</t>
+        </is>
+      </c>
       <c r="V4" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="b">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT50AD+B</t>
+          <t>DIN_69871:SK40</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>2.62</v>
+      </c>
       <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
         <v>1</v>
       </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2021/YG1-TOOLING</t>
-        </is>
+      <c r="AK4" t="n">
+        <v>341.37</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>27983.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK40-TPM830</t>
+          <t>SK40-VER40-115</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -879,19 +929,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Патроны для резьбонарезания с осевой компенсацией SK-TPM со сменными втулками с предохранительной муфтой</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="F5" t="n">
-        <v>143.6</v>
-      </c>
+          <t>Патроны SK-VER для синхронизированного резьбонарезания</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>115</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -905,12 +953,12 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>DER_BRC-830</t>
+          <t>DER_BLC-40</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>DER_TPD:830</t>
+          <t>DER_VER:40</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -919,13 +967,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -943,7 +991,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -955,12 +1003,26 @@
         <is>
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>188.04</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>15414.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HSK100A-VER25-91</t>
+          <t>DCK5-VER20-50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -970,17 +1032,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Патроны HSK-A-VER для синхронизированного резьбонарезания</t>
+          <t>Патроны DCK-VER для синхронизированного резьбонарезания</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -994,12 +1056,12 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>DER_BLC-25</t>
+          <t>DER_BLC-20</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>DER_VER:25</t>
+          <t>DER_VER:20</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1008,13 +1070,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="W6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1026,13 +1088,13 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ISO_12164_1_2013:HSK100A</t>
+          <t>DER_DCK:5</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>3.95</v>
+        <v>0.65</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1044,6 +1106,20 @@
         <is>
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>13662.59</v>
       </c>
     </row>
   </sheetData>
